--- a/docs/src/reference/data-dictionaries/Z_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/Z_Dict.xlsx
@@ -7861,12 +7861,12 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr"/>
@@ -7925,12 +7925,12 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr"/>
@@ -7968,7 +7968,11 @@
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
@@ -7989,12 +7993,12 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr"/>
@@ -8053,12 +8057,12 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr"/>
@@ -8117,12 +8121,12 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr"/>
@@ -8181,12 +8185,12 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr"/>
@@ -8249,12 +8253,12 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr"/>
@@ -8292,7 +8296,11 @@
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T102" t="inlineStr">
         <is>
           <t>x</t>
@@ -8317,12 +8325,12 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
@@ -8385,12 +8393,12 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr"/>
@@ -8449,12 +8457,12 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr"/>
@@ -8513,12 +8521,12 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr"/>
@@ -8556,7 +8564,11 @@
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr">
@@ -8577,12 +8589,12 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr"/>
@@ -8641,12 +8653,12 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr"/>
@@ -8705,12 +8717,12 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr"/>
@@ -8769,12 +8781,12 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr"/>
@@ -8837,12 +8849,12 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr"/>
@@ -8880,7 +8892,11 @@
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T111" t="inlineStr">
         <is>
           <t>x</t>
@@ -8905,12 +8921,12 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr"/>
@@ -8973,12 +8989,12 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr"/>
@@ -9037,12 +9053,12 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr"/>
@@ -9101,12 +9117,12 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr"/>
@@ -9165,12 +9181,12 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr"/>
@@ -9208,7 +9224,11 @@
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr">
@@ -9229,12 +9249,12 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr"/>
@@ -9293,12 +9313,12 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr"/>
@@ -9357,12 +9377,12 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr"/>
@@ -9421,12 +9441,12 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr"/>
@@ -9489,12 +9509,12 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr"/>
@@ -9532,7 +9552,11 @@
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T121" t="inlineStr">
         <is>
           <t>x</t>
@@ -9557,12 +9581,12 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr"/>
@@ -9625,12 +9649,12 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr"/>
@@ -9668,7 +9692,11 @@
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr">
@@ -9689,12 +9717,12 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr"/>
@@ -9753,12 +9781,12 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr"/>
@@ -9796,7 +9824,11 @@
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T125" t="inlineStr">
         <is>
           <t>x</t>
@@ -9821,12 +9853,12 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/Z_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/Z_Dict.xlsx
@@ -7665,12 +7665,12 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>CovidCareMap, 2020</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr"/>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>CovidCareMap, 2020</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr"/>
@@ -7797,12 +7797,12 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>CovidCareMap, 2020</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr"/>
@@ -10092,7 +10092,11 @@
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
@@ -10113,12 +10117,12 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr"/>
@@ -10177,12 +10181,12 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr"/>
@@ -10220,7 +10224,11 @@
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T131" t="inlineStr">
         <is>
           <t>x</t>
@@ -10245,12 +10253,12 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/Z_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/Z_Dict.xlsx
@@ -7644,7 +7644,11 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr">
@@ -7708,7 +7712,11 @@
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
@@ -7772,7 +7780,11 @@
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T94" t="inlineStr">
         <is>
           <t>x</t>
@@ -7840,7 +7852,11 @@
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
@@ -7904,7 +7920,11 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
@@ -8036,7 +8056,11 @@
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
@@ -8100,7 +8124,11 @@
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
@@ -8164,7 +8192,11 @@
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
@@ -8228,7 +8260,11 @@
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T101" t="inlineStr">
         <is>
           <t>x</t>
@@ -8368,7 +8404,11 @@
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T103" t="inlineStr">
         <is>
           <t>x</t>
@@ -8436,7 +8476,11 @@
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr">
@@ -8500,7 +8544,11 @@
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
@@ -8632,7 +8680,11 @@
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
@@ -8696,7 +8748,11 @@
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
@@ -8760,7 +8816,11 @@
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
@@ -8824,7 +8884,11 @@
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T110" t="inlineStr">
         <is>
           <t>x</t>
@@ -8964,7 +9028,11 @@
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T112" t="inlineStr">
         <is>
           <t>x</t>
@@ -9032,7 +9100,11 @@
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
@@ -9096,7 +9168,11 @@
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
@@ -9160,7 +9236,11 @@
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
@@ -9292,7 +9372,11 @@
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
@@ -9356,7 +9440,11 @@
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
@@ -9420,7 +9508,11 @@
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">
@@ -9484,7 +9576,11 @@
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T120" t="inlineStr">
         <is>
           <t>x</t>
@@ -9624,7 +9720,11 @@
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T122" t="inlineStr">
         <is>
           <t>x</t>
@@ -9760,7 +9860,11 @@
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
@@ -9896,7 +10000,11 @@
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
@@ -9960,7 +10068,11 @@
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
@@ -10024,7 +10136,11 @@
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T128" t="inlineStr">
         <is>
           <t>x</t>
@@ -10296,7 +10412,11 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
@@ -10360,7 +10480,11 @@
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
@@ -10424,7 +10548,11 @@
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T134" t="inlineStr">
         <is>
           <t>x</t>
@@ -10560,7 +10688,11 @@
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">

--- a/docs/src/reference/data-dictionaries/Z_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/Z_Dict.xlsx
@@ -10025,12 +10025,12 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr"/>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr"/>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/Z_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/Z_Dict.xlsx
@@ -10437,12 +10437,12 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr"/>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr"/>
@@ -10577,12 +10577,12 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/Z_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/Z_Dict.xlsx
@@ -10276,7 +10276,11 @@
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr"/>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">

--- a/docs/src/reference/data-dictionaries/Z_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/Z_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD157"/>
+  <dimension ref="A1:AD169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -894,7 +894,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>% Persons aged 25 years and over with a bachelor’s degree as their highest level of education</t>
+          <t>% Bachelor's degree</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -982,7 +982,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>% Population aged 25 years and over whose highest educational attainment is a high school diploma (or equivalent)</t>
+          <t>% High School Graduate</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>% Population aged 25 years and over with less than a high school diploma</t>
+          <t>% No High School Diploma</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Proportion of the population aged 5+ who speak a language other than English at home but are proficient in English</t>
+          <t xml:space="preserve">% English Proficiency </t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>% Population aged 25 years and over with a graduate or professional degree</t>
+          <t>% Graduate or Professional Degree</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>% Population 25 years and over with some college, but no degree</t>
+          <t>% Some College, but No Degree</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Proportion of occupied housing units that are considered crowded (more than 1 person per room)</t>
+          <t>Crowded Housing</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -7635,11 +7635,7 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
@@ -7653,28 +7649,28 @@
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr">
         <is>
-          <t>HospCntDr</t>
+          <t>HivCntDr</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>Count of Hospitals (30-min drive)</t>
+          <t>Count of HIV Providers</t>
         </is>
       </c>
       <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr"/>
@@ -7689,7 +7685,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -7703,11 +7699,7 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
@@ -7721,28 +7713,28 @@
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>HospMinDis</t>
+          <t>HivMinDis</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Hospital</t>
+          <t>Distance to nearest HIV Provider</t>
         </is>
       </c>
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr"/>
@@ -7757,7 +7749,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -7771,11 +7763,7 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
@@ -7785,36 +7773,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>HospTmDr</t>
+          <t>HivTmDr</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Hospital</t>
+          <t>Driving time to nearest HIV Provider</t>
         </is>
       </c>
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr"/>
@@ -7829,7 +7813,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -7843,11 +7827,7 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
@@ -7861,28 +7841,28 @@
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
-          <t>BupCntBk30</t>
+          <t>HivTmDr2</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min bike)</t>
+          <t>Driving time (min) to nearest HIV Testing Facility, with impedance</t>
         </is>
       </c>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr"/>
@@ -7897,7 +7877,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -7929,28 +7909,28 @@
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
-          <t>BupCntBk60</t>
+          <t>HospCntDr</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (60-min bike)</t>
+          <t>Count of Hospitals (30-min drive)</t>
         </is>
       </c>
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr"/>
@@ -7965,7 +7945,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -7997,28 +7977,28 @@
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>BupCntDr30</t>
+          <t>HospMinDis</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min drive)</t>
+          <t>Distance (mi) to nearest Hospital</t>
         </is>
       </c>
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr"/>
@@ -8033,7 +8013,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -8061,32 +8041,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr"/>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>BupCntWk30</t>
+          <t>HospTmDr</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min walk)</t>
+          <t>Driving time (min) to nearest Hospital</t>
         </is>
       </c>
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr"/>
@@ -8101,7 +8085,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -8115,11 +8099,7 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
@@ -8133,28 +8113,28 @@
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>BupCntWk60</t>
+          <t>HospTmDr2</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (60-min walk)</t>
+          <t>Driving time (min) to nearest Hospital with Impedance Factor</t>
         </is>
       </c>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr"/>
@@ -8201,12 +8181,12 @@
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>BupMinDis</t>
+          <t>BupCntBk30</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Buprenorphine Provider</t>
+          <t>Count of Buprenorphine Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X100" t="inlineStr"/>
@@ -8265,20 +8245,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
         <is>
-          <t>BupTmBk</t>
+          <t>BupCntBk60</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Count of Buprenorphine Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X101" t="inlineStr"/>
@@ -8337,20 +8313,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr">
         <is>
-          <t>BupTmDr</t>
+          <t>BupCntDr30</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
+          <t>Count of Buprenorphine Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X102" t="inlineStr"/>
@@ -8409,20 +8381,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>BupTmWk</t>
+          <t>BupCntWk30</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Count of Buprenorphine Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X103" t="inlineStr"/>
@@ -8485,12 +8453,12 @@
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr">
         <is>
-          <t>MetCntBk30</t>
+          <t>BupCntWk60</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>Count of methadone providers (30-min bike)</t>
+          <t>Count of Buprenorphine Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X104" t="inlineStr"/>
@@ -8553,12 +8521,12 @@
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
         <is>
-          <t>MetCntBk60</t>
+          <t>BupMinDis</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min bike)</t>
+          <t>Distance (mi) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X105" t="inlineStr"/>
@@ -8617,16 +8585,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr"/>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr">
         <is>
-          <t>MetCntDr30</t>
+          <t>BupTmBk</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min drive)</t>
+          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X106" t="inlineStr"/>
@@ -8685,16 +8657,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T107" t="inlineStr"/>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
         <is>
-          <t>MetCntWk30</t>
+          <t>BupTmDr</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min walk)</t>
+          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X107" t="inlineStr"/>
@@ -8753,16 +8729,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T108" t="inlineStr"/>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
         <is>
-          <t>MetCntWk60</t>
+          <t>BupTmWk</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min walk)</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X108" t="inlineStr"/>
@@ -8825,12 +8805,12 @@
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>MetMinDis</t>
+          <t>MetCntBk30</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Methadone Provider</t>
+          <t>Count of methadone providers (30-min bike)</t>
         </is>
       </c>
       <c r="X109" t="inlineStr"/>
@@ -8889,20 +8869,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr">
         <is>
-          <t>MetTmBk</t>
+          <t>MetCntBk60</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Count of Methadone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X110" t="inlineStr"/>
@@ -8961,20 +8937,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>MetTmDr</t>
+          <t>MetCntDr30</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Count of Methadone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
@@ -9033,20 +9005,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>MetTmWk</t>
+          <t>MetCntWk30</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Count of Methadone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X112" t="inlineStr"/>
@@ -9109,12 +9077,12 @@
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>MoudMinDis</t>
+          <t>MetCntWk60</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest MOUD (any)</t>
+          <t>Count of Methadone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X113" t="inlineStr"/>
@@ -9177,12 +9145,12 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
         <is>
-          <t>NaltCntBk30</t>
+          <t>MetMinDis</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min bike)</t>
+          <t>Distance (mi) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X114" t="inlineStr"/>
@@ -9241,16 +9209,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T115" t="inlineStr"/>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>NaltCntBk60</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min bike)</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -9309,16 +9281,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T116" t="inlineStr"/>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr">
         <is>
-          <t>NaltCntDr30</t>
+          <t>MetTmDr</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min drive)</t>
+          <t>Driving Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -9377,16 +9353,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T117" t="inlineStr"/>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>NaltCntWk30</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min walk)</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -9449,12 +9429,12 @@
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>NaltCntWk60</t>
+          <t>MoudMinDis</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min walk)</t>
+          <t>Distance (mi) to nearest MOUD (any)</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -9517,12 +9497,12 @@
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">
         <is>
-          <t>NaltMinDis</t>
+          <t>NaltCntBk30</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Naltrexone Provider</t>
+          <t>Count of Naltrexone Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X119" t="inlineStr"/>
@@ -9581,20 +9561,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltCntBk60</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Count of Naltrexone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X120" t="inlineStr"/>
@@ -9653,20 +9629,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltCntDr30</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Count of Naltrexone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X121" t="inlineStr"/>
@@ -9725,20 +9697,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
         <is>
-          <t>NaltTmWk</t>
+          <t>NaltCntWk30</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Count of Naltrexone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X122" t="inlineStr"/>
@@ -9783,12 +9751,12 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
@@ -9801,12 +9769,12 @@
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr">
         <is>
-          <t>OtpCntDr</t>
+          <t>NaltCntWk60</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
+          <t>Count of Naltrexone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X123" t="inlineStr"/>
@@ -9851,12 +9819,12 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
@@ -9869,12 +9837,12 @@
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
         <is>
-          <t>OtpMinDis</t>
+          <t>NaltMinDis</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Distance to nearest OTP</t>
+          <t>Distance (mi) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
@@ -9919,12 +9887,12 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
@@ -9941,12 +9909,12 @@
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>OtpTmDr</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
@@ -9977,7 +9945,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -10005,32 +9973,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T126" t="inlineStr"/>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>MhCntDr</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Count of Mental Health Providers (30-min drive)</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr"/>
@@ -10045,7 +10017,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -10073,32 +10045,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr"/>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>MhMinDis</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Mental Health Provider</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr"/>
@@ -10113,7 +10089,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -10127,12 +10103,12 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
@@ -10141,36 +10117,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>MhTmDr</t>
+          <t>OtpCntDr</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr"/>
@@ -10185,7 +10157,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -10198,13 +10170,13 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
@@ -10217,28 +10189,28 @@
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
         <is>
-          <t>RxCntDr</t>
+          <t>OtpMinDis</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Count of Pharmacies (30-min drive)</t>
+          <t>Distance to nearest OTP</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr"/>
@@ -10253,7 +10225,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -10266,13 +10238,13 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
@@ -10281,32 +10253,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T130" t="inlineStr"/>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
         <is>
-          <t>RxMinDis</t>
+          <t>OtpTmDr</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Pharmacy</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr"/>
@@ -10321,7 +10297,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -10334,12 +10310,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
@@ -10349,36 +10325,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
         <is>
-          <t>RxTmDr</t>
+          <t>MhCntDr</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy</t>
+          <t>Count of Mental Health Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr"/>
@@ -10393,7 +10365,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -10425,18 +10397,18 @@
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
         <is>
-          <t>SutCntDr</t>
+          <t>MhMinDis</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
+          <t>Distance (mi) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
@@ -10461,7 +10433,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -10489,22 +10461,26 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T133" t="inlineStr"/>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
         <is>
-          <t>SutMinDis</t>
+          <t>MhTmDr</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
@@ -10529,7 +10505,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -10543,11 +10519,7 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
@@ -10557,26 +10529,22 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
         <is>
-          <t>SutTmDr</t>
+          <t>MhTmDr2</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
+          <t>Driving time (min) to nearest Mental Health Provider with impedance</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
@@ -10601,7 +10569,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -10614,12 +10582,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
@@ -10633,28 +10601,28 @@
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>RxCntDr</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Count of Pharmacies (30-min drive)</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr"/>
@@ -10669,7 +10637,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -10682,12 +10650,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
@@ -10701,28 +10669,28 @@
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>RxMinDis</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Distance (mi) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr"/>
@@ -10737,7 +10705,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -10750,12 +10718,12 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
@@ -10773,28 +10741,28 @@
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>RxTmDr</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Driving Time (min) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr"/>
@@ -10809,17 +10777,13 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
@@ -10832,33 +10796,37 @@
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>Ruca1</t>
+          <t>RxTmDr2</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Primary RUCA Code</t>
+          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr"/>
@@ -10873,17 +10841,13 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
@@ -10891,38 +10855,46 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>Ruca2</t>
+          <t>SutCntDr</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Secondary RUCA Code</t>
+          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -10937,17 +10909,13 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
@@ -10955,42 +10923,46 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>Rurality</t>
+          <t>SutMinDis</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Urban-Suburban-Rural</t>
+          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -11000,12 +10972,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -11017,44 +10989,52 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr"/>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>SutTmDr</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr"/>
@@ -11064,12 +11044,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -11081,11 +11061,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
@@ -11094,39 +11070,39 @@
       </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -11136,12 +11112,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -11153,11 +11129,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
@@ -11166,39 +11138,39 @@
       </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr"/>
@@ -11208,12 +11180,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -11225,11 +11197,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
@@ -11238,39 +11206,43 @@
       </c>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr"/>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
@@ -11280,12 +11252,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -11297,52 +11269,48 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr"/>
-      <c r="T145" t="inlineStr"/>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -11352,12 +11320,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -11369,52 +11337,44 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>HcvCntDr</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Count of HCV Providers</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr"/>
@@ -11424,73 +11384,61 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr"/>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>HcvMinDis</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Distance to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr"/>
@@ -11500,12 +11448,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -11518,43 +11466,43 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>HcvTmDr</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Driving time to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr"/>
@@ -11564,73 +11512,61 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>HcvTmDr2</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr"/>
@@ -11640,12 +11576,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -11661,52 +11597,40 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>Ruca1</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Primary RUCA Code</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -11716,29 +11640,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Urban/Suburban/Rural Classification</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>x</t>
@@ -11749,56 +11661,40 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>Ruca2</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Secondary RUCA Code</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr"/>
@@ -11808,29 +11704,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Urban/Suburban/Rural Classification</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>x</t>
@@ -11841,56 +11725,44 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr"/>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>Rurality</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Urban-Suburban-Rural</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr"/>
@@ -11900,12 +11772,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -11923,17 +11795,9 @@
         </is>
       </c>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr"/>
@@ -11941,28 +11805,28 @@
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
@@ -11972,12 +11836,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -12001,44 +11865,40 @@
         </is>
       </c>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr"/>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr"/>
@@ -12048,12 +11908,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -12077,40 +11937,40 @@
         </is>
       </c>
       <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
@@ -12120,12 +11980,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -12149,40 +12009,40 @@
         </is>
       </c>
       <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
@@ -12192,12 +12052,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -12221,49 +12081,961 @@
         </is>
       </c>
       <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr"/>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
       <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Employment Trends</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>TotWrkE</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Count of Working Population</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr"/>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>ACS 2018, 2023</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr"/>
+      <c r="AC158" t="inlineStr"/>
+      <c r="AD158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>GiniCoeff</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Income Inequality (Gini Coefficient)</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr"/>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>HUD 2018; ACS 2012, 2018</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr"/>
+      <c r="AC159" t="inlineStr"/>
+      <c r="AD159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Internet Access</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>NoIntP</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Households without Internet Access %</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr"/>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>ACS 2019</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr"/>
+      <c r="AC160" t="inlineStr"/>
+      <c r="AD160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>MedInc</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Median Income</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr"/>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr"/>
+      <c r="AC161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>PciE</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Per Capita Income</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr"/>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr"/>
+      <c r="AC162" t="inlineStr"/>
+      <c r="AD162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>PovP</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Poverty %</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr"/>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr"/>
+      <c r="AC163" t="inlineStr"/>
+      <c r="AD163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>UnempP</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Unemployment %</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr"/>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr"/>
+      <c r="AC164" t="inlineStr"/>
+      <c r="AD164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SviSmryRnk</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr"/>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr"/>
+      <c r="AD165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>SviTh1</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 1</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr"/>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr"/>
+      <c r="AD166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SviTh2</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 2</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr"/>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr"/>
+      <c r="AC167" t="inlineStr"/>
+      <c r="AD167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr"/>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr"/>
+      <c r="AC168" t="inlineStr"/>
+      <c r="AD168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/Z_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/Z_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD169"/>
+  <dimension ref="A1:AD174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8715,11 +8715,7 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
@@ -8737,12 +8733,12 @@
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
         <is>
-          <t>BupTmWk</t>
+          <t>BupTmDr2</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Driving time to nearest buprenorphine provider (with impedance)</t>
         </is>
       </c>
       <c r="X108" t="inlineStr"/>
@@ -8801,16 +8797,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr"/>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>MetCntBk30</t>
+          <t>BupTmWk</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Count of methadone providers (30-min bike)</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X109" t="inlineStr"/>
@@ -8873,12 +8873,12 @@
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr">
         <is>
-          <t>MetCntBk60</t>
+          <t>MetCntBk30</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min bike)</t>
+          <t>Count of methadone providers (30-min bike)</t>
         </is>
       </c>
       <c r="X110" t="inlineStr"/>
@@ -8941,12 +8941,12 @@
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>MetCntDr30</t>
+          <t>MetCntBk60</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min drive)</t>
+          <t>Count of Methadone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
@@ -9009,12 +9009,12 @@
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>MetCntWk30</t>
+          <t>MetCntDr30</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min walk)</t>
+          <t>Count of Methadone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X112" t="inlineStr"/>
@@ -9077,12 +9077,12 @@
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>MetCntWk60</t>
+          <t>MetCntWk30</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min walk)</t>
+          <t>Count of Methadone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X113" t="inlineStr"/>
@@ -9145,12 +9145,12 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
         <is>
-          <t>MetMinDis</t>
+          <t>MetCntWk60</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Methadone Provider</t>
+          <t>Count of Methadone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X114" t="inlineStr"/>
@@ -9209,20 +9209,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>MetTmBk</t>
+          <t>MetMinDis</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Distance (mi) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -9289,12 +9285,12 @@
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr">
         <is>
-          <t>MetTmDr</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -9361,12 +9357,12 @@
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>MetTmWk</t>
+          <t>MetTmDr</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Driving Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -9411,11 +9407,7 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
@@ -9425,16 +9417,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T118" t="inlineStr"/>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>MoudMinDis</t>
+          <t>MetTmDr2</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest MOUD (any)</t>
+          <t>Driving time to nearest methadone provider (with impedance)</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -9493,16 +9489,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr"/>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">
         <is>
-          <t>NaltCntBk30</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min bike)</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X119" t="inlineStr"/>
@@ -9565,12 +9565,12 @@
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr">
         <is>
-          <t>NaltCntBk60</t>
+          <t>MoudMinDis</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min bike)</t>
+          <t>Distance (mi) to nearest MOUD (any)</t>
         </is>
       </c>
       <c r="X120" t="inlineStr"/>
@@ -9633,12 +9633,12 @@
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr">
         <is>
-          <t>NaltCntDr30</t>
+          <t>NaltCntBk30</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min drive)</t>
+          <t>Count of Naltrexone Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X121" t="inlineStr"/>
@@ -9701,12 +9701,12 @@
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
         <is>
-          <t>NaltCntWk30</t>
+          <t>NaltCntBk60</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min walk)</t>
+          <t>Count of Naltrexone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X122" t="inlineStr"/>
@@ -9769,12 +9769,12 @@
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr">
         <is>
-          <t>NaltCntWk60</t>
+          <t>NaltCntDr30</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min walk)</t>
+          <t>Count of Naltrexone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X123" t="inlineStr"/>
@@ -9837,12 +9837,12 @@
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
         <is>
-          <t>NaltMinDis</t>
+          <t>NaltCntWk30</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Naltrexone Provider</t>
+          <t>Count of Naltrexone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
@@ -9901,20 +9901,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltCntWk60</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Count of Naltrexone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
@@ -9973,20 +9969,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltMinDis</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Distance (mi) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
@@ -10053,12 +10045,12 @@
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>NaltTmWk</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
@@ -10103,12 +10095,12 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
@@ -10117,16 +10109,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr"/>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>OtpCntDr</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
@@ -10172,11 +10168,7 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
@@ -10189,12 +10181,12 @@
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
         <is>
-          <t>OtpMinDis</t>
+          <t>NaltTmDr2</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Distance to nearest OTP</t>
+          <t>Driving time to nearest naltrexone provider (with impedance)</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
@@ -10239,12 +10231,12 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
@@ -10261,12 +10253,12 @@
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
         <is>
-          <t>OtpTmDr</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -10297,7 +10289,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -10311,12 +10303,12 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
@@ -10329,28 +10321,28 @@
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
         <is>
-          <t>MhCntDr</t>
+          <t>OtpCntDr</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>Count of Mental Health Providers (30-min drive)</t>
+          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr"/>
@@ -10365,7 +10357,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -10379,12 +10371,12 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
@@ -10397,28 +10389,28 @@
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
         <is>
-          <t>MhMinDis</t>
+          <t>OtpMinDis</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Mental Health Provider</t>
+          <t>Distance to nearest OTP</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr"/>
@@ -10433,7 +10425,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -10447,12 +10439,12 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
@@ -10469,28 +10461,28 @@
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
         <is>
-          <t>MhTmDr</t>
+          <t>OtpTmDr</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr"/>
@@ -10505,7 +10497,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -10533,28 +10525,28 @@
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
         <is>
-          <t>MhTmDr2</t>
+          <t>OtpTmDr2</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Mental Health Provider with impedance</t>
+          <t>Driving time to nearest OTP (impedance-adjusted)</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr"/>
@@ -10569,7 +10561,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -10582,12 +10574,12 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
@@ -10601,28 +10593,28 @@
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>RxCntDr</t>
+          <t>MhCntDr</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Count of Pharmacies (30-min drive)</t>
+          <t>Count of Mental Health Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr"/>
@@ -10637,7 +10629,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -10650,12 +10642,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
@@ -10669,28 +10661,28 @@
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>RxMinDis</t>
+          <t>MhMinDis</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Pharmacy</t>
+          <t>Distance (mi) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr"/>
@@ -10705,7 +10697,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -10718,12 +10710,12 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
@@ -10741,28 +10733,28 @@
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>RxTmDr</t>
+          <t>MhTmDr</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr"/>
@@ -10777,7 +10769,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -10805,28 +10797,28 @@
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>RxTmDr2</t>
+          <t>MhTmDr2</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Driving time (min) to nearest Mental Health Provider with impedance</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr"/>
@@ -10841,7 +10833,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -10854,12 +10846,12 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
@@ -10873,28 +10865,28 @@
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SutCntDr</t>
+          <t>RxCntDr</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
+          <t>Count of Pharmacies (30-min drive)</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -10909,7 +10901,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -10922,12 +10914,12 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
@@ -10941,28 +10933,28 @@
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>SutMinDis</t>
+          <t>RxMinDis</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
+          <t>Distance (mi) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -10977,7 +10969,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -10990,12 +10982,12 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
@@ -11013,28 +11005,28 @@
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>SutTmDr</t>
+          <t>RxTmDr</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
+          <t>Driving Time (min) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr"/>
@@ -11049,7 +11041,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -11063,11 +11055,7 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
@@ -11081,28 +11069,28 @@
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>RxTmDr2</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -11117,7 +11105,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -11149,28 +11137,28 @@
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>SutCntDr</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr"/>
@@ -11185,7 +11173,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -11213,36 +11201,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>SutMinDis</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
@@ -11257,7 +11241,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -11271,7 +11255,11 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
@@ -11289,28 +11277,28 @@
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>FqhcTmDr2</t>
+          <t>SutTmDr</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
+          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -11325,7 +11313,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -11353,28 +11341,28 @@
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>HcvCntDr</t>
+          <t>SutTmDr2</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Count of HCV Providers</t>
+          <t>Driving time to nearest Substance Use Treatment Provider (with impedance)</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr"/>
@@ -11389,7 +11377,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -11403,7 +11391,11 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
@@ -11417,28 +11409,28 @@
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>HcvMinDis</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Distance to nearest HCV Provider</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr"/>
@@ -11453,7 +11445,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -11467,7 +11459,11 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
@@ -11481,28 +11477,28 @@
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>HcvTmDr</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Driving time to nearest HCV Provider</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr"/>
@@ -11517,7 +11513,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -11531,7 +11527,11 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
@@ -11541,32 +11541,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T149" t="inlineStr"/>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>HcvTmDr2</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr"/>
@@ -11581,17 +11585,13 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
@@ -11604,33 +11604,41 @@
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr"/>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>Ruca1</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Primary RUCA Code</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -11645,17 +11653,13 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
@@ -11668,33 +11672,37 @@
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>Ruca2</t>
+          <t>HcvCntDr</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Secondary RUCA Code</t>
+          <t>Count of HCV Providers</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr"/>
@@ -11709,17 +11717,13 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
@@ -11732,37 +11736,37 @@
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>Rurality</t>
+          <t>HcvMinDis</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Urban-Suburban-Rural</t>
+          <t>Distance to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr"/>
@@ -11772,12 +11776,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -11789,44 +11793,44 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr"/>
-      <c r="S153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>HcvTmDr</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Driving time to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
@@ -11836,12 +11840,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -11853,52 +11857,44 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>HcvTmDr2</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr"/>
@@ -11908,69 +11904,61 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>Ruca1</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Primary RUCA Code</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
@@ -11980,69 +11968,61 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>Ruca2</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Secondary RUCA Code</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
@@ -12052,69 +12032,65 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr"/>
-      <c r="T157" t="inlineStr"/>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>Rurality</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Urban-Suburban-Rural</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
@@ -12147,30 +12123,22 @@
         </is>
       </c>
       <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
@@ -12201,17 +12169,13 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
@@ -12241,28 +12205,28 @@
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr"/>
@@ -12277,7 +12241,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -12289,44 +12253,52 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr"/>
@@ -12341,17 +12313,13 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -12381,28 +12349,28 @@
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
@@ -12417,17 +12385,13 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
@@ -12457,28 +12421,28 @@
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr"/>
@@ -12493,29 +12457,13 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Employment Trends</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
@@ -12542,35 +12490,31 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
@@ -12585,24 +12529,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>x</t>
@@ -12634,35 +12566,31 @@
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr"/>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
@@ -12672,12 +12600,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -12689,23 +12617,15 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr"/>
@@ -12713,28 +12633,28 @@
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr"/>
@@ -12744,18 +12664,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
@@ -12773,44 +12697,40 @@
         </is>
       </c>
       <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr"/>
-      <c r="T166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
@@ -12820,18 +12740,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
@@ -12849,40 +12773,40 @@
         </is>
       </c>
       <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr"/>
@@ -12892,18 +12816,34 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -12921,40 +12861,44 @@
         </is>
       </c>
       <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
-      <c r="U168" t="inlineStr"/>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr"/>
@@ -12964,18 +12908,34 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -12993,49 +12953,417 @@
         </is>
       </c>
       <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr"/>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>
       <c r="AC169" t="inlineStr"/>
       <c r="AD169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SviSmryRnk</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr"/>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SviTh1</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 1</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr"/>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr"/>
+      <c r="AC171" t="inlineStr"/>
+      <c r="AD171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
+      <c r="S172" t="inlineStr"/>
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>SviTh2</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 2</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr"/>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr"/>
+      <c r="AC172" t="inlineStr"/>
+      <c r="AD172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
+      <c r="S173" t="inlineStr"/>
+      <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr"/>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr"/>
+      <c r="AC173" t="inlineStr"/>
+      <c r="AD173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr"/>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr"/>
+      <c r="AC174" t="inlineStr"/>
+      <c r="AD174" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/Z_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/Z_Dict.xlsx
@@ -5014,7 +5014,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Count Black/African American Populationw</t>
+          <t>Count Black/African American Population</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>% Black/African American Populationw</t>
+          <t>% Black/African American Population</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/Z_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/Z_Dict.xlsx
@@ -2986,7 +2986,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>% Population: Age 15-44</t>
+          <t>Population: Age 15-44 (count)</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>% Population: Age 15-44</t>
+          <t>% Population: Age 15-44 (percent)</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>% Population: Age 65+</t>
+          <t>Population: Age 65+ (count)</t>
         </is>
       </c>
       <c r="X46" t="inlineStr"/>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>% Population: Age 65+</t>
+          <t>% Population: Age 65+ (percent)</t>
         </is>
       </c>
       <c r="X47" t="inlineStr"/>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Biking Time (min) to nearest Buprenorphine Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X106" t="inlineStr"/>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
+          <t>Driving Time (min) to nearest Buprenorphine Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X107" t="inlineStr"/>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X109" t="inlineStr"/>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Biking Time (min) to nearest Methadone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Driving Time (min) to nearest Methadone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Walking Time (min) to nearest Methadone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X119" t="inlineStr"/>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP) (tract/ZIP)</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Driving Time (min) to nearest Mental Health Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/Z_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/Z_Dict.xlsx
@@ -8738,7 +8738,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Driving time to nearest buprenorphine provider (with impedance)</t>
+          <t>Driving Time (min) to Nearest Buprenorphine Provider (with impedance)</t>
         </is>
       </c>
       <c r="X108" t="inlineStr"/>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Driving time to nearest methadone provider (with impedance)</t>
+          <t>Driving Time (min) to Nearest Methadone Provider (with impedance)</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Driving time to nearest naltrexone provider (with impedance)</t>
+          <t>Driving Time (min) to Nearest Naltrexone Provider (with impedance)</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Driving time to nearest OTP (impedance-adjusted)</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP), with impedance</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/Z_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/Z_Dict.xlsx
@@ -11927,7 +11927,11 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
@@ -11953,12 +11957,12 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>USDA-ERS 2010; ACS 2018, USDA-ERS 2020</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate; United States Department of Agriculture Economic Research Service, 2020</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
@@ -11991,7 +11995,11 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
@@ -12017,12 +12025,12 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>USDA-ERS 2010; ACS 2018, USDA-ERS 2020</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate; United States Department of Agriculture Economic Research Service, 2020</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
@@ -12055,7 +12063,11 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
@@ -12085,12 +12097,12 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>USDA-ERS 2010; ACS 2018, USDA-ERS 2020</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate; United States Department of Agriculture Economic Research Service, 2020</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
